--- a/campaigns/LeshyBachelor_2026/pack_001/review/stage6_review.xlsx
+++ b/campaigns/LeshyBachelor_2026/pack_001/review/stage6_review.xlsx
@@ -1900,7 +1900,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Найди Турка</t>
+          <t>Найди Турку</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Получи синий бутон для бутоньерки</t>
+          <t>Получи Синюю розу</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr"/>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Создай Приличное зелье первого впечатления</t>
+          <t>Создай Приличное зелье</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Попроси у друзей розовую мерную ложечку</t>
+          <t>Попроси у друзей Розовую мерную ложечку</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Найди ароматную каплю для котла</t>
+          <t>Найди Разлитый коктейль</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr"/>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Получи синюю болотную ленту</t>
+          <t>Получи Синюю розу</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr"/>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>Создай Набор для романтического похода</t>
+          <t>Создай Набор</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr"/>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>Попроси у друзей заплатку</t>
+          <t>Попроси у друзей Заплатку</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>Найди серебряную застёжку для фляги</t>
+          <t>Найди Родированное серебро</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr"/>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="E419" s="4" t="inlineStr">
         <is>
-          <t>Собери Роза дома</t>
+          <t>Собери Розу дома</t>
         </is>
       </c>
       <c r="F419" s="4" t="inlineStr"/>
@@ -18206,7 +18206,7 @@
       </c>
       <c r="E448" s="4" t="inlineStr">
         <is>
-          <t>Создай Тихий шалаш для двоих</t>
+          <t>Создай Тихий шалаш</t>
         </is>
       </c>
       <c r="F448" s="4" t="inlineStr"/>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="E461" s="4" t="inlineStr">
         <is>
-          <t>Попроси у друзей занавеску</t>
+          <t>Попроси у друзей Занавеску</t>
         </is>
       </c>
       <c r="F461" s="4" t="inlineStr"/>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="E473" s="4" t="inlineStr">
         <is>
-          <t>Получи семицветный огонёк для шалаша</t>
+          <t>Получи Ландыш</t>
         </is>
       </c>
       <c r="F473" s="4" t="inlineStr"/>
@@ -21840,7 +21840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:S82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21848,12 +21848,20 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21872,6 +21880,14 @@
       <c r="I1" s="4" t="n"/>
       <c r="J1" s="4" t="n"/>
       <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -21913,6 +21929,14 @@
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
@@ -21950,6 +21974,14 @@
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr"/>
@@ -21975,7 +22007,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Спрятанные камеры на пнях</t>
+          <t>Спрятанные камеры</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr"/>
@@ -21983,6 +22015,14 @@
       <c r="I4" s="1" t="n"/>
       <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="n"/>
+      <c r="L4" s="1" t="n"/>
+      <c r="M4" s="1" t="n"/>
+      <c r="N4" s="1" t="n"/>
+      <c r="O4" s="1" t="n"/>
+      <c r="P4" s="1" t="n"/>
+      <c r="Q4" s="1" t="n"/>
+      <c r="R4" s="1" t="n"/>
+      <c r="S4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr"/>
@@ -22008,7 +22048,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Болотные украшения Кикиморы</t>
+          <t>Болотные украшения</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr"/>
@@ -22016,6 +22056,14 @@
       <c r="I5" s="1" t="n"/>
       <c r="J5" s="1" t="n"/>
       <c r="K5" s="1" t="n"/>
+      <c r="L5" s="1" t="n"/>
+      <c r="M5" s="1" t="n"/>
+      <c r="N5" s="1" t="n"/>
+      <c r="O5" s="1" t="n"/>
+      <c r="P5" s="1" t="n"/>
+      <c r="Q5" s="1" t="n"/>
+      <c r="R5" s="1" t="n"/>
+      <c r="S5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr"/>
@@ -22041,7 +22089,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Промокший микрофон Русалки</t>
+          <t>Промокший микрофон</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr"/>
@@ -22049,6 +22097,14 @@
       <c r="I6" s="1" t="n"/>
       <c r="J6" s="1" t="n"/>
       <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
+      <c r="P6" s="1" t="n"/>
+      <c r="Q6" s="1" t="n"/>
+      <c r="R6" s="1" t="n"/>
+      <c r="S6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr"/>
@@ -22074,7 +22130,7 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Рекламные таблички Шапокляк</t>
+          <t>Рекламные таблички</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr"/>
@@ -22082,6 +22138,14 @@
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
       <c r="K7" s="1" t="n"/>
+      <c r="L7" s="1" t="n"/>
+      <c r="M7" s="1" t="n"/>
+      <c r="N7" s="1" t="n"/>
+      <c r="O7" s="1" t="n"/>
+      <c r="P7" s="1" t="n"/>
+      <c r="Q7" s="1" t="n"/>
+      <c r="R7" s="1" t="n"/>
+      <c r="S7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr"/>
@@ -22107,7 +22171,7 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>Правильные розы среди шиповника</t>
+          <t>Правильные розы</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr"/>
@@ -22115,6 +22179,14 @@
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="n"/>
       <c r="K8" s="1" t="n"/>
+      <c r="L8" s="1" t="n"/>
+      <c r="M8" s="1" t="n"/>
+      <c r="N8" s="1" t="n"/>
+      <c r="O8" s="1" t="n"/>
+      <c r="P8" s="1" t="n"/>
+      <c r="Q8" s="1" t="n"/>
+      <c r="R8" s="1" t="n"/>
+      <c r="S8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -22128,6 +22200,14 @@
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="n"/>
       <c r="K9" s="1" t="n"/>
+      <c r="L9" s="1" t="n"/>
+      <c r="M9" s="1" t="n"/>
+      <c r="N9" s="1" t="n"/>
+      <c r="O9" s="1" t="n"/>
+      <c r="P9" s="1" t="n"/>
+      <c r="Q9" s="1" t="n"/>
+      <c r="R9" s="1" t="n"/>
+      <c r="S9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr"/>
@@ -22145,6 +22225,14 @@
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -22194,6 +22282,14 @@
       </c>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr"/>
@@ -22239,6 +22335,14 @@
       </c>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr"/>
@@ -22264,7 +22368,7 @@
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>синий бутон для бутоньерки</t>
+          <t>Синий бутон</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -22280,6 +22384,14 @@
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="n"/>
       <c r="K13" s="1" t="n"/>
+      <c r="L13" s="1" t="n"/>
+      <c r="M13" s="1" t="n"/>
+      <c r="N13" s="1" t="n"/>
+      <c r="O13" s="1" t="n"/>
+      <c r="P13" s="1" t="n"/>
+      <c r="Q13" s="1" t="n"/>
+      <c r="R13" s="1" t="n"/>
+      <c r="S13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr"/>
@@ -22305,7 +22417,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ароматную каплю для котла</t>
+          <t>Ароматная капля</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -22321,6 +22433,14 @@
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="n"/>
       <c r="K14" s="1" t="n"/>
+      <c r="L14" s="1" t="n"/>
+      <c r="M14" s="1" t="n"/>
+      <c r="N14" s="1" t="n"/>
+      <c r="O14" s="1" t="n"/>
+      <c r="P14" s="1" t="n"/>
+      <c r="Q14" s="1" t="n"/>
+      <c r="R14" s="1" t="n"/>
+      <c r="S14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr"/>
@@ -22346,7 +22466,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>синяя болотная лента</t>
+          <t>Синяя лента</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
@@ -22362,6 +22482,14 @@
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="n"/>
       <c r="K15" s="1" t="n"/>
+      <c r="L15" s="1" t="n"/>
+      <c r="M15" s="1" t="n"/>
+      <c r="N15" s="1" t="n"/>
+      <c r="O15" s="1" t="n"/>
+      <c r="P15" s="1" t="n"/>
+      <c r="Q15" s="1" t="n"/>
+      <c r="R15" s="1" t="n"/>
+      <c r="S15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr"/>
@@ -22387,7 +22515,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>серебряную застёжку для фляги</t>
+          <t>Серебряная застёжка</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -22403,6 +22531,14 @@
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="n"/>
       <c r="K16" s="1" t="n"/>
+      <c r="L16" s="1" t="n"/>
+      <c r="M16" s="1" t="n"/>
+      <c r="N16" s="1" t="n"/>
+      <c r="O16" s="1" t="n"/>
+      <c r="P16" s="1" t="n"/>
+      <c r="Q16" s="1" t="n"/>
+      <c r="R16" s="1" t="n"/>
+      <c r="S16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr"/>
@@ -22428,7 +22564,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>семицветный огонёк для шалаша</t>
+          <t>Мягкий настил</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
@@ -22444,6 +22580,14 @@
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="n"/>
       <c r="K17" s="1" t="n"/>
+      <c r="L17" s="1" t="n"/>
+      <c r="M17" s="1" t="n"/>
+      <c r="N17" s="1" t="n"/>
+      <c r="O17" s="1" t="n"/>
+      <c r="P17" s="1" t="n"/>
+      <c r="Q17" s="1" t="n"/>
+      <c r="R17" s="1" t="n"/>
+      <c r="S17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -22457,6 +22601,14 @@
       <c r="I18" s="1" t="n"/>
       <c r="J18" s="1" t="n"/>
       <c r="K18" s="1" t="n"/>
+      <c r="L18" s="1" t="n"/>
+      <c r="M18" s="1" t="n"/>
+      <c r="N18" s="1" t="n"/>
+      <c r="O18" s="1" t="n"/>
+      <c r="P18" s="1" t="n"/>
+      <c r="Q18" s="1" t="n"/>
+      <c r="R18" s="1" t="n"/>
+      <c r="S18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
@@ -22474,6 +22626,14 @@
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -22531,6 +22691,14 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr"/>
@@ -22584,6 +22752,14 @@
           <t>id</t>
         </is>
       </c>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr"/>
@@ -22629,6 +22805,14 @@
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr"/>
+      <c r="L22" s="1" t="n"/>
+      <c r="M22" s="1" t="n"/>
+      <c r="N22" s="1" t="n"/>
+      <c r="O22" s="1" t="n"/>
+      <c r="P22" s="1" t="n"/>
+      <c r="Q22" s="1" t="n"/>
+      <c r="R22" s="1" t="n"/>
+      <c r="S22" s="1" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr"/>
@@ -22674,6 +22858,14 @@
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr"/>
+      <c r="L23" s="1" t="n"/>
+      <c r="M23" s="1" t="n"/>
+      <c r="N23" s="1" t="n"/>
+      <c r="O23" s="1" t="n"/>
+      <c r="P23" s="1" t="n"/>
+      <c r="Q23" s="1" t="n"/>
+      <c r="R23" s="1" t="n"/>
+      <c r="S23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr"/>
@@ -22719,6 +22911,14 @@
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr"/>
+      <c r="L24" s="1" t="n"/>
+      <c r="M24" s="1" t="n"/>
+      <c r="N24" s="1" t="n"/>
+      <c r="O24" s="1" t="n"/>
+      <c r="P24" s="1" t="n"/>
+      <c r="Q24" s="1" t="n"/>
+      <c r="R24" s="1" t="n"/>
+      <c r="S24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr"/>
@@ -22764,6 +22964,14 @@
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr"/>
+      <c r="L25" s="1" t="n"/>
+      <c r="M25" s="1" t="n"/>
+      <c r="N25" s="1" t="n"/>
+      <c r="O25" s="1" t="n"/>
+      <c r="P25" s="1" t="n"/>
+      <c r="Q25" s="1" t="n"/>
+      <c r="R25" s="1" t="n"/>
+      <c r="S25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr"/>
@@ -22809,6 +23017,14 @@
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr"/>
+      <c r="L26" s="1" t="n"/>
+      <c r="M26" s="1" t="n"/>
+      <c r="N26" s="1" t="n"/>
+      <c r="O26" s="1" t="n"/>
+      <c r="P26" s="1" t="n"/>
+      <c r="Q26" s="1" t="n"/>
+      <c r="R26" s="1" t="n"/>
+      <c r="S26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -22822,6 +23038,14 @@
       <c r="I27" s="1" t="n"/>
       <c r="J27" s="1" t="n"/>
       <c r="K27" s="1" t="n"/>
+      <c r="L27" s="1" t="n"/>
+      <c r="M27" s="1" t="n"/>
+      <c r="N27" s="1" t="n"/>
+      <c r="O27" s="1" t="n"/>
+      <c r="P27" s="1" t="n"/>
+      <c r="Q27" s="1" t="n"/>
+      <c r="R27" s="1" t="n"/>
+      <c r="S27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr"/>
@@ -22839,6 +23063,14 @@
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="4" t="n"/>
+      <c r="R28" s="4" t="n"/>
+      <c r="S28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -22896,6 +23128,14 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr"/>
@@ -22949,6 +23189,14 @@
           <t>id</t>
         </is>
       </c>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr"/>
@@ -22974,7 +23222,7 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>синий бутон для бутоньерки</t>
+          <t>Синий бутон</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
@@ -22998,6 +23246,14 @@
         </is>
       </c>
       <c r="K31" s="1" t="inlineStr"/>
+      <c r="L31" s="1" t="n"/>
+      <c r="M31" s="1" t="n"/>
+      <c r="N31" s="1" t="n"/>
+      <c r="O31" s="1" t="n"/>
+      <c r="P31" s="1" t="n"/>
+      <c r="Q31" s="1" t="n"/>
+      <c r="R31" s="1" t="n"/>
+      <c r="S31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr"/>
@@ -23023,7 +23279,7 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>ароматную каплю для котла</t>
+          <t>Ароматная капля</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
@@ -23047,6 +23303,14 @@
         </is>
       </c>
       <c r="K32" s="1" t="inlineStr"/>
+      <c r="L32" s="1" t="n"/>
+      <c r="M32" s="1" t="n"/>
+      <c r="N32" s="1" t="n"/>
+      <c r="O32" s="1" t="n"/>
+      <c r="P32" s="1" t="n"/>
+      <c r="Q32" s="1" t="n"/>
+      <c r="R32" s="1" t="n"/>
+      <c r="S32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr"/>
@@ -23072,7 +23336,7 @@
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>синяя болотная лента</t>
+          <t>Синяя лента</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
@@ -23096,6 +23360,14 @@
         </is>
       </c>
       <c r="K33" s="1" t="inlineStr"/>
+      <c r="L33" s="1" t="n"/>
+      <c r="M33" s="1" t="n"/>
+      <c r="N33" s="1" t="n"/>
+      <c r="O33" s="1" t="n"/>
+      <c r="P33" s="1" t="n"/>
+      <c r="Q33" s="1" t="n"/>
+      <c r="R33" s="1" t="n"/>
+      <c r="S33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr"/>
@@ -23121,7 +23393,7 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>серебряную застёжку для фляги</t>
+          <t>Серебряная застёжка</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -23145,6 +23417,14 @@
         </is>
       </c>
       <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="n"/>
+      <c r="M34" s="1" t="n"/>
+      <c r="N34" s="1" t="n"/>
+      <c r="O34" s="1" t="n"/>
+      <c r="P34" s="1" t="n"/>
+      <c r="Q34" s="1" t="n"/>
+      <c r="R34" s="1" t="n"/>
+      <c r="S34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr"/>
@@ -23170,7 +23450,7 @@
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>семицветный огонёк для шалаша</t>
+          <t>Мягкий настил</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -23194,6 +23474,14 @@
         </is>
       </c>
       <c r="K35" s="1" t="inlineStr"/>
+      <c r="L35" s="1" t="n"/>
+      <c r="M35" s="1" t="n"/>
+      <c r="N35" s="1" t="n"/>
+      <c r="O35" s="1" t="n"/>
+      <c r="P35" s="1" t="n"/>
+      <c r="Q35" s="1" t="n"/>
+      <c r="R35" s="1" t="n"/>
+      <c r="S35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
@@ -23207,6 +23495,14 @@
       <c r="I36" s="1" t="n"/>
       <c r="J36" s="1" t="n"/>
       <c r="K36" s="1" t="n"/>
+      <c r="L36" s="1" t="n"/>
+      <c r="M36" s="1" t="n"/>
+      <c r="N36" s="1" t="n"/>
+      <c r="O36" s="1" t="n"/>
+      <c r="P36" s="1" t="n"/>
+      <c r="Q36" s="1" t="n"/>
+      <c r="R36" s="1" t="n"/>
+      <c r="S36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr"/>
@@ -23224,6 +23520,14 @@
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n"/>
+      <c r="S37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -23277,6 +23581,14 @@
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr"/>
@@ -23326,6 +23638,14 @@
         </is>
       </c>
       <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr"/>
@@ -23351,7 +23671,7 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>розовую мерную ложечку</t>
+          <t>Розовая ложечка</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -23367,6 +23687,14 @@
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="n"/>
+      <c r="L40" s="1" t="n"/>
+      <c r="M40" s="1" t="n"/>
+      <c r="N40" s="1" t="n"/>
+      <c r="O40" s="1" t="n"/>
+      <c r="P40" s="1" t="n"/>
+      <c r="Q40" s="1" t="n"/>
+      <c r="R40" s="1" t="n"/>
+      <c r="S40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr"/>
@@ -23392,7 +23720,7 @@
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>занавеску</t>
+          <t>Занавеска</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
@@ -23408,6 +23736,14 @@
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="n"/>
+      <c r="L41" s="1" t="n"/>
+      <c r="M41" s="1" t="n"/>
+      <c r="N41" s="1" t="n"/>
+      <c r="O41" s="1" t="n"/>
+      <c r="P41" s="1" t="n"/>
+      <c r="Q41" s="1" t="n"/>
+      <c r="R41" s="1" t="n"/>
+      <c r="S41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
@@ -23421,6 +23757,14 @@
       <c r="I42" s="1" t="n"/>
       <c r="J42" s="1" t="n"/>
       <c r="K42" s="1" t="n"/>
+      <c r="L42" s="1" t="n"/>
+      <c r="M42" s="1" t="n"/>
+      <c r="N42" s="1" t="n"/>
+      <c r="O42" s="1" t="n"/>
+      <c r="P42" s="1" t="n"/>
+      <c r="Q42" s="1" t="n"/>
+      <c r="R42" s="1" t="n"/>
+      <c r="S42" s="1" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr"/>
@@ -23438,6 +23782,14 @@
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="4" t="n"/>
+      <c r="R43" s="4" t="n"/>
+      <c r="S43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -23495,6 +23847,14 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr"/>
@@ -23548,6 +23908,14 @@
           <t>id</t>
         </is>
       </c>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n"/>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr"/>
@@ -23573,7 +23941,7 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>розовую мерную ложечку</t>
+          <t>Розовая ложечка</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -23597,6 +23965,14 @@
         </is>
       </c>
       <c r="K46" s="1" t="inlineStr"/>
+      <c r="L46" s="1" t="n"/>
+      <c r="M46" s="1" t="n"/>
+      <c r="N46" s="1" t="n"/>
+      <c r="O46" s="1" t="n"/>
+      <c r="P46" s="1" t="n"/>
+      <c r="Q46" s="1" t="n"/>
+      <c r="R46" s="1" t="n"/>
+      <c r="S46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr"/>
@@ -23622,7 +23998,7 @@
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>занавеску</t>
+          <t>Занавеска</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -23646,6 +24022,14 @@
         </is>
       </c>
       <c r="K47" s="1" t="inlineStr"/>
+      <c r="L47" s="1" t="n"/>
+      <c r="M47" s="1" t="n"/>
+      <c r="N47" s="1" t="n"/>
+      <c r="O47" s="1" t="n"/>
+      <c r="P47" s="1" t="n"/>
+      <c r="Q47" s="1" t="n"/>
+      <c r="R47" s="1" t="n"/>
+      <c r="S47" s="1" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
@@ -23659,6 +24043,14 @@
       <c r="I48" s="1" t="n"/>
       <c r="J48" s="1" t="n"/>
       <c r="K48" s="1" t="n"/>
+      <c r="L48" s="1" t="n"/>
+      <c r="M48" s="1" t="n"/>
+      <c r="N48" s="1" t="n"/>
+      <c r="O48" s="1" t="n"/>
+      <c r="P48" s="1" t="n"/>
+      <c r="Q48" s="1" t="n"/>
+      <c r="R48" s="1" t="n"/>
+      <c r="S48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr"/>
@@ -23676,6 +24068,14 @@
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
+      <c r="Q49" s="4" t="n"/>
+      <c r="R49" s="4" t="n"/>
+      <c r="S49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -23733,6 +24133,14 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
+      <c r="Q50" s="2" t="n"/>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr"/>
@@ -23786,6 +24194,14 @@
           <t>id</t>
         </is>
       </c>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="3" t="n"/>
+      <c r="Q51" s="3" t="n"/>
+      <c r="R51" s="3" t="n"/>
+      <c r="S51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr"/>
@@ -23811,7 +24227,7 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>розовую мерную ложечку</t>
+          <t>Розовая ложечка</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -23835,6 +24251,14 @@
         </is>
       </c>
       <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="n"/>
+      <c r="M52" s="1" t="n"/>
+      <c r="N52" s="1" t="n"/>
+      <c r="O52" s="1" t="n"/>
+      <c r="P52" s="1" t="n"/>
+      <c r="Q52" s="1" t="n"/>
+      <c r="R52" s="1" t="n"/>
+      <c r="S52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr"/>
@@ -23860,7 +24284,7 @@
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>занавеску</t>
+          <t>Занавеска</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
@@ -23884,6 +24308,14 @@
         </is>
       </c>
       <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="n"/>
+      <c r="M53" s="1" t="n"/>
+      <c r="N53" s="1" t="n"/>
+      <c r="O53" s="1" t="n"/>
+      <c r="P53" s="1" t="n"/>
+      <c r="Q53" s="1" t="n"/>
+      <c r="R53" s="1" t="n"/>
+      <c r="S53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
@@ -23897,6 +24329,14 @@
       <c r="I54" s="1" t="n"/>
       <c r="J54" s="1" t="n"/>
       <c r="K54" s="1" t="n"/>
+      <c r="L54" s="1" t="n"/>
+      <c r="M54" s="1" t="n"/>
+      <c r="N54" s="1" t="n"/>
+      <c r="O54" s="1" t="n"/>
+      <c r="P54" s="1" t="n"/>
+      <c r="Q54" s="1" t="n"/>
+      <c r="R54" s="1" t="n"/>
+      <c r="S54" s="1" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr"/>
@@ -23914,6 +24354,14 @@
       <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n"/>
+      <c r="R55" s="4" t="n"/>
+      <c r="S55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -23967,6 +24415,14 @@
         </is>
       </c>
       <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
+      <c r="R56" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr"/>
@@ -24016,6 +24472,14 @@
         </is>
       </c>
       <c r="K57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="n"/>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="3" t="n"/>
+      <c r="Q57" s="3" t="n"/>
+      <c r="R57" s="3" t="n"/>
+      <c r="S57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr"/>
@@ -24041,7 +24505,7 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>заплатку</t>
+          <t>Заплатка</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -24057,6 +24521,14 @@
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="n"/>
+      <c r="L58" s="1" t="n"/>
+      <c r="M58" s="1" t="n"/>
+      <c r="N58" s="1" t="n"/>
+      <c r="O58" s="1" t="n"/>
+      <c r="P58" s="1" t="n"/>
+      <c r="Q58" s="1" t="n"/>
+      <c r="R58" s="1" t="n"/>
+      <c r="S58" s="1" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
@@ -24070,6 +24542,14 @@
       <c r="I59" s="1" t="n"/>
       <c r="J59" s="1" t="n"/>
       <c r="K59" s="1" t="n"/>
+      <c r="L59" s="1" t="n"/>
+      <c r="M59" s="1" t="n"/>
+      <c r="N59" s="1" t="n"/>
+      <c r="O59" s="1" t="n"/>
+      <c r="P59" s="1" t="n"/>
+      <c r="Q59" s="1" t="n"/>
+      <c r="R59" s="1" t="n"/>
+      <c r="S59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr"/>
@@ -24087,6 +24567,14 @@
       <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n"/>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="4" t="n"/>
+      <c r="R60" s="4" t="n"/>
+      <c r="S60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -24144,6 +24632,14 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="n"/>
+      <c r="Q61" s="2" t="n"/>
+      <c r="R61" s="2" t="n"/>
+      <c r="S61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr"/>
@@ -24197,6 +24693,14 @@
           <t>id</t>
         </is>
       </c>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
+      <c r="Q62" s="3" t="n"/>
+      <c r="R62" s="3" t="n"/>
+      <c r="S62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr"/>
@@ -24222,7 +24726,7 @@
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>заплатку</t>
+          <t>Заплатка</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
@@ -24246,6 +24750,14 @@
         </is>
       </c>
       <c r="K63" s="1" t="inlineStr"/>
+      <c r="L63" s="1" t="n"/>
+      <c r="M63" s="1" t="n"/>
+      <c r="N63" s="1" t="n"/>
+      <c r="O63" s="1" t="n"/>
+      <c r="P63" s="1" t="n"/>
+      <c r="Q63" s="1" t="n"/>
+      <c r="R63" s="1" t="n"/>
+      <c r="S63" s="1" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
@@ -24259,6 +24771,14 @@
       <c r="I64" s="1" t="n"/>
       <c r="J64" s="1" t="n"/>
       <c r="K64" s="1" t="n"/>
+      <c r="L64" s="1" t="n"/>
+      <c r="M64" s="1" t="n"/>
+      <c r="N64" s="1" t="n"/>
+      <c r="O64" s="1" t="n"/>
+      <c r="P64" s="1" t="n"/>
+      <c r="Q64" s="1" t="n"/>
+      <c r="R64" s="1" t="n"/>
+      <c r="S64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr"/>
@@ -24276,6 +24796,14 @@
       <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="4" t="n"/>
+      <c r="R65" s="4" t="n"/>
+      <c r="S65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -24333,6 +24861,14 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
+      <c r="Q66" s="2" t="n"/>
+      <c r="R66" s="2" t="n"/>
+      <c r="S66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr"/>
@@ -24386,6 +24922,14 @@
           <t>id</t>
         </is>
       </c>
+      <c r="L67" s="3" t="n"/>
+      <c r="M67" s="3" t="n"/>
+      <c r="N67" s="3" t="n"/>
+      <c r="O67" s="3" t="n"/>
+      <c r="P67" s="3" t="n"/>
+      <c r="Q67" s="3" t="n"/>
+      <c r="R67" s="3" t="n"/>
+      <c r="S67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr"/>
@@ -24411,7 +24955,7 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>заплатку</t>
+          <t>Заплатка</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
@@ -24435,6 +24979,14 @@
         </is>
       </c>
       <c r="K68" s="1" t="inlineStr"/>
+      <c r="L68" s="1" t="n"/>
+      <c r="M68" s="1" t="n"/>
+      <c r="N68" s="1" t="n"/>
+      <c r="O68" s="1" t="n"/>
+      <c r="P68" s="1" t="n"/>
+      <c r="Q68" s="1" t="n"/>
+      <c r="R68" s="1" t="n"/>
+      <c r="S68" s="1" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
@@ -24448,6 +25000,14 @@
       <c r="I69" s="1" t="n"/>
       <c r="J69" s="1" t="n"/>
       <c r="K69" s="1" t="n"/>
+      <c r="L69" s="1" t="n"/>
+      <c r="M69" s="1" t="n"/>
+      <c r="N69" s="1" t="n"/>
+      <c r="O69" s="1" t="n"/>
+      <c r="P69" s="1" t="n"/>
+      <c r="Q69" s="1" t="n"/>
+      <c r="R69" s="1" t="n"/>
+      <c r="S69" s="1" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr"/>
@@ -24465,6 +25025,14 @@
       <c r="I70" s="4" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
+      <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="4" t="n"/>
+      <c r="S70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -24518,6 +25086,14 @@
         </is>
       </c>
       <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="n"/>
+      <c r="Q71" s="2" t="n"/>
+      <c r="R71" s="2" t="n"/>
+      <c r="S71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr"/>
@@ -24567,6 +25143,14 @@
         </is>
       </c>
       <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
+      <c r="O72" s="3" t="n"/>
+      <c r="P72" s="3" t="n"/>
+      <c r="Q72" s="3" t="n"/>
+      <c r="R72" s="3" t="n"/>
+      <c r="S72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr"/>
@@ -24592,7 +25176,7 @@
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>Приличное зелье первого впечатления</t>
+          <t>Приличное зелье</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
@@ -24608,6 +25192,14 @@
       </c>
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="n"/>
+      <c r="L73" s="1" t="n"/>
+      <c r="M73" s="1" t="n"/>
+      <c r="N73" s="1" t="n"/>
+      <c r="O73" s="1" t="n"/>
+      <c r="P73" s="1" t="n"/>
+      <c r="Q73" s="1" t="n"/>
+      <c r="R73" s="1" t="n"/>
+      <c r="S73" s="1" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr"/>
@@ -24633,7 +25225,7 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>Набор для романтического похода</t>
+          <t>Набор</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
@@ -24649,6 +25241,14 @@
       </c>
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="n"/>
+      <c r="L74" s="1" t="n"/>
+      <c r="M74" s="1" t="n"/>
+      <c r="N74" s="1" t="n"/>
+      <c r="O74" s="1" t="n"/>
+      <c r="P74" s="1" t="n"/>
+      <c r="Q74" s="1" t="n"/>
+      <c r="R74" s="1" t="n"/>
+      <c r="S74" s="1" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr"/>
@@ -24674,7 +25274,7 @@
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>Тихий шалаш для двоих</t>
+          <t>Тихий шалаш</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
@@ -24690,6 +25290,513 @@
       </c>
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="n"/>
+      <c r="L75" s="1" t="n"/>
+      <c r="M75" s="1" t="n"/>
+      <c r="N75" s="1" t="n"/>
+      <c r="O75" s="1" t="n"/>
+      <c r="P75" s="1" t="n"/>
+      <c r="Q75" s="1" t="n"/>
+      <c r="R75" s="1" t="n"/>
+      <c r="S75" s="1" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n"/>
+      <c r="B76" s="1" t="n"/>
+      <c r="C76" s="1" t="n"/>
+      <c r="D76" s="1" t="n"/>
+      <c r="E76" s="1" t="n"/>
+      <c r="F76" s="1" t="n"/>
+      <c r="G76" s="1" t="n"/>
+      <c r="H76" s="1" t="n"/>
+      <c r="I76" s="1" t="n"/>
+      <c r="J76" s="1" t="n"/>
+      <c r="K76" s="1" t="n"/>
+      <c r="L76" s="1" t="n"/>
+      <c r="M76" s="1" t="n"/>
+      <c r="N76" s="1" t="n"/>
+      <c r="O76" s="1" t="n"/>
+      <c r="P76" s="1" t="n"/>
+      <c r="Q76" s="1" t="n"/>
+      <c r="R76" s="1" t="n"/>
+      <c r="S76" s="1" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr"/>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Рецепты 4 ингридиента</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr"/>
+      <c r="M77" s="4" t="inlineStr"/>
+      <c r="N77" s="4" t="inlineStr"/>
+      <c r="O77" s="4" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr"/>
+      <c r="Q77" s="4" t="inlineStr"/>
+      <c r="R77" s="4" t="inlineStr"/>
+      <c r="S77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>temp_01</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr"/>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>lifespan</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>ingredients</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_1_asset</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_1_asset_amount</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_2_asset</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_2_asset_amount</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_3_asset</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_3_asset_amount</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_4_asset</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>ingredient_4_asset_amount</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>conditions</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr"/>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>/recipe/Dacha_2025/Dacha_2025_R_1_Recipe.proto.js</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>/recipe/LeshyBachelor_2026/LeshyBachelor_2026_R_1_Recipe.proto.js</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_R_1_Recipe</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_R_1</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>asset=LeshyBachelor_2026_ASK_1:10+asset=LeshyBachelor_2026_GR_2:40+asset=LeshyBachelor_2026_Story_RandomRecipe_1_R_1:1+asset=LeshyBachelor_2026_Story_FA_2:1</t>
+        </is>
+      </c>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_ASK_1</t>
+        </is>
+      </c>
+      <c r="J80" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K80" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_GR_2</t>
+        </is>
+      </c>
+      <c r="L80" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M80" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_Story_RandomRecipe_1_R_1</t>
+        </is>
+      </c>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_Story_FA_2</t>
+        </is>
+      </c>
+      <c r="P80" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q80" s="1" t="inlineStr">
+        <is>
+          <t>active_quest=LeshyBachelor_2026_Story_3+asset!=LeshyBachelor_2026_R_1:1</t>
+        </is>
+      </c>
+      <c r="R80" s="1" t="inlineStr">
+        <is>
+          <t>asset=LeshyBachelor_2026_R_1:1</t>
+        </is>
+      </c>
+      <c r="S80" s="1" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr"/>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>/recipe/Dacha_2025/Dacha_2025_R_1_Recipe.proto.js</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>/recipe/LeshyBachelor_2026/LeshyBachelor_2026_R_2_Recipe.proto.js</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_R_2_Recipe</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_R_2</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>asset=LeshyBachelor_2026_PER_1:10+asset=LeshyBachelor_2026_GR_4:40+asset=LeshyBachelor_2026_Chest_1_R_1:1+asset=LeshyBachelor_2026_Story_RandomRecipe_1_R_1:1</t>
+        </is>
+      </c>
+      <c r="I81" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_PER_1</t>
+        </is>
+      </c>
+      <c r="J81" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K81" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_GR_4</t>
+        </is>
+      </c>
+      <c r="L81" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M81" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_Chest_1_R_1</t>
+        </is>
+      </c>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O81" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_Story_RandomRecipe_1_R_1</t>
+        </is>
+      </c>
+      <c r="P81" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q81" s="1" t="inlineStr">
+        <is>
+          <t>active_quest=LeshyBachelor_2026_Story_7+asset!=LeshyBachelor_2026_R_2:1</t>
+        </is>
+      </c>
+      <c r="R81" s="1" t="inlineStr">
+        <is>
+          <t>asset=LeshyBachelor_2026_R_2:1</t>
+        </is>
+      </c>
+      <c r="S81" s="1" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr"/>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>/recipe/Dacha_2025/Dacha_2025_R_1_Recipe.proto.js</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>/recipe/LeshyBachelor_2026/LeshyBachelor_2026_R_3_Recipe.proto.js</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_R_3_Recipe</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_R_3</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>asset=LeshyBachelor_2026_ASK_2:10+asset=LeshyBachelor_2026_GR_5:80+asset=LeshyBachelor_2026_Story_FA_2:1+asset=LeshyBachelor_2026_Chest_1_R_1:1</t>
+        </is>
+      </c>
+      <c r="I82" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_ASK_2</t>
+        </is>
+      </c>
+      <c r="J82" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K82" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_GR_5</t>
+        </is>
+      </c>
+      <c r="L82" s="1" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M82" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_Story_FA_2</t>
+        </is>
+      </c>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="inlineStr">
+        <is>
+          <t>LeshyBachelor_2026_Chest_1_R_1</t>
+        </is>
+      </c>
+      <c r="P82" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q82" s="1" t="inlineStr">
+        <is>
+          <t>active_quest=LeshyBachelor_2026_Story_11+asset!=LeshyBachelor_2026_R_3:1</t>
+        </is>
+      </c>
+      <c r="R82" s="1" t="inlineStr">
+        <is>
+          <t>asset=LeshyBachelor_2026_R_3:1</t>
+        </is>
+      </c>
+      <c r="S82" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/campaigns/LeshyBachelor_2026/pack_001/review/stage6_review.xlsx
+++ b/campaigns/LeshyBachelor_2026/pack_001/review/stage6_review.xlsx
@@ -1900,7 +1900,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Найди Турку</t>
+          <t>Найди Турка</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Получи Синюю розу</t>
+          <t>Получи синий бутон для бутоньерки</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr"/>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Создай Приличное зелье</t>
+          <t>Создай Приличное зелье первого впечатления</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Попроси у друзей Розовую мерную ложечку</t>
+          <t>Попроси у друзей розовую мерную ложечку</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Найди Разлитый коктейль</t>
+          <t>Найди ароматную каплю для котла</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr"/>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Получи Синюю розу</t>
+          <t>Получи синюю болотную ленту</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr"/>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>Создай Набор</t>
+          <t>Создай Набор для романтического похода</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr"/>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>Попроси у друзей Заплатку</t>
+          <t>Попроси у друзей заплатку</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>Найди Родированное серебро</t>
+          <t>Найди серебряную застёжку для фляги</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr"/>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="E419" s="4" t="inlineStr">
         <is>
-          <t>Собери Розу дома</t>
+          <t>Собери Роза дома</t>
         </is>
       </c>
       <c r="F419" s="4" t="inlineStr"/>
@@ -18206,7 +18206,7 @@
       </c>
       <c r="E448" s="4" t="inlineStr">
         <is>
-          <t>Создай Тихий шалаш</t>
+          <t>Создай Тихий шалаш для двоих</t>
         </is>
       </c>
       <c r="F448" s="4" t="inlineStr"/>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="E461" s="4" t="inlineStr">
         <is>
-          <t>Попроси у друзей Занавеску</t>
+          <t>Попроси у друзей занавеску</t>
         </is>
       </c>
       <c r="F461" s="4" t="inlineStr"/>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="E473" s="4" t="inlineStr">
         <is>
-          <t>Получи Ландыш</t>
+          <t>Получи семицветный огонёк для шалаша</t>
         </is>
       </c>
       <c r="F473" s="4" t="inlineStr"/>
@@ -21840,7 +21840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21848,20 +21848,12 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="27" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21880,14 +21872,6 @@
       <c r="I1" s="4" t="n"/>
       <c r="J1" s="4" t="n"/>
       <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="4" t="n"/>
-      <c r="O1" s="4" t="n"/>
-      <c r="P1" s="4" t="n"/>
-      <c r="Q1" s="4" t="n"/>
-      <c r="R1" s="4" t="n"/>
-      <c r="S1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -21929,14 +21913,6 @@
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
@@ -21974,14 +21950,6 @@
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr"/>
@@ -22007,7 +21975,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Спрятанные камеры</t>
+          <t>Спрятанные камеры на пнях</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr"/>
@@ -22015,14 +21983,6 @@
       <c r="I4" s="1" t="n"/>
       <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
-      <c r="Q4" s="1" t="n"/>
-      <c r="R4" s="1" t="n"/>
-      <c r="S4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr"/>
@@ -22048,7 +22008,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Болотные украшения</t>
+          <t>Болотные украшения Кикиморы</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr"/>
@@ -22056,14 +22016,6 @@
       <c r="I5" s="1" t="n"/>
       <c r="J5" s="1" t="n"/>
       <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-      <c r="O5" s="1" t="n"/>
-      <c r="P5" s="1" t="n"/>
-      <c r="Q5" s="1" t="n"/>
-      <c r="R5" s="1" t="n"/>
-      <c r="S5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr"/>
@@ -22089,7 +22041,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Промокший микрофон</t>
+          <t>Промокший микрофон Русалки</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr"/>
@@ -22097,14 +22049,6 @@
       <c r="I6" s="1" t="n"/>
       <c r="J6" s="1" t="n"/>
       <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
-      <c r="N6" s="1" t="n"/>
-      <c r="O6" s="1" t="n"/>
-      <c r="P6" s="1" t="n"/>
-      <c r="Q6" s="1" t="n"/>
-      <c r="R6" s="1" t="n"/>
-      <c r="S6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr"/>
@@ -22130,7 +22074,7 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Рекламные таблички</t>
+          <t>Рекламные таблички Шапокляк</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr"/>
@@ -22138,14 +22082,6 @@
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
       <c r="K7" s="1" t="n"/>
-      <c r="L7" s="1" t="n"/>
-      <c r="M7" s="1" t="n"/>
-      <c r="N7" s="1" t="n"/>
-      <c r="O7" s="1" t="n"/>
-      <c r="P7" s="1" t="n"/>
-      <c r="Q7" s="1" t="n"/>
-      <c r="R7" s="1" t="n"/>
-      <c r="S7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr"/>
@@ -22171,7 +22107,7 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>Правильные розы</t>
+          <t>Правильные розы среди шиповника</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr"/>
@@ -22179,14 +22115,6 @@
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="n"/>
       <c r="K8" s="1" t="n"/>
-      <c r="L8" s="1" t="n"/>
-      <c r="M8" s="1" t="n"/>
-      <c r="N8" s="1" t="n"/>
-      <c r="O8" s="1" t="n"/>
-      <c r="P8" s="1" t="n"/>
-      <c r="Q8" s="1" t="n"/>
-      <c r="R8" s="1" t="n"/>
-      <c r="S8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -22200,14 +22128,6 @@
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="n"/>
       <c r="K9" s="1" t="n"/>
-      <c r="L9" s="1" t="n"/>
-      <c r="M9" s="1" t="n"/>
-      <c r="N9" s="1" t="n"/>
-      <c r="O9" s="1" t="n"/>
-      <c r="P9" s="1" t="n"/>
-      <c r="Q9" s="1" t="n"/>
-      <c r="R9" s="1" t="n"/>
-      <c r="S9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr"/>
@@ -22225,14 +22145,6 @@
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -22282,14 +22194,6 @@
       </c>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr"/>
@@ -22335,14 +22239,6 @@
       </c>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
-      <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr"/>
@@ -22368,7 +22264,7 @@
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>Синий бутон</t>
+          <t>синий бутон для бутоньерки</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -22384,14 +22280,6 @@
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="n"/>
       <c r="K13" s="1" t="n"/>
-      <c r="L13" s="1" t="n"/>
-      <c r="M13" s="1" t="n"/>
-      <c r="N13" s="1" t="n"/>
-      <c r="O13" s="1" t="n"/>
-      <c r="P13" s="1" t="n"/>
-      <c r="Q13" s="1" t="n"/>
-      <c r="R13" s="1" t="n"/>
-      <c r="S13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr"/>
@@ -22417,7 +22305,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>Ароматная капля</t>
+          <t>ароматную каплю для котла</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -22433,14 +22321,6 @@
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="n"/>
       <c r="K14" s="1" t="n"/>
-      <c r="L14" s="1" t="n"/>
-      <c r="M14" s="1" t="n"/>
-      <c r="N14" s="1" t="n"/>
-      <c r="O14" s="1" t="n"/>
-      <c r="P14" s="1" t="n"/>
-      <c r="Q14" s="1" t="n"/>
-      <c r="R14" s="1" t="n"/>
-      <c r="S14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr"/>
@@ -22466,7 +22346,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Синяя лента</t>
+          <t>синяя болотная лента</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
@@ -22482,14 +22362,6 @@
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="n"/>
       <c r="K15" s="1" t="n"/>
-      <c r="L15" s="1" t="n"/>
-      <c r="M15" s="1" t="n"/>
-      <c r="N15" s="1" t="n"/>
-      <c r="O15" s="1" t="n"/>
-      <c r="P15" s="1" t="n"/>
-      <c r="Q15" s="1" t="n"/>
-      <c r="R15" s="1" t="n"/>
-      <c r="S15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr"/>
@@ -22515,7 +22387,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Серебряная застёжка</t>
+          <t>серебряную застёжку для фляги</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -22531,14 +22403,6 @@
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="n"/>
       <c r="K16" s="1" t="n"/>
-      <c r="L16" s="1" t="n"/>
-      <c r="M16" s="1" t="n"/>
-      <c r="N16" s="1" t="n"/>
-      <c r="O16" s="1" t="n"/>
-      <c r="P16" s="1" t="n"/>
-      <c r="Q16" s="1" t="n"/>
-      <c r="R16" s="1" t="n"/>
-      <c r="S16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr"/>
@@ -22564,7 +22428,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Мягкий настил</t>
+          <t>семицветный огонёк для шалаша</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
@@ -22580,14 +22444,6 @@
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="n"/>
       <c r="K17" s="1" t="n"/>
-      <c r="L17" s="1" t="n"/>
-      <c r="M17" s="1" t="n"/>
-      <c r="N17" s="1" t="n"/>
-      <c r="O17" s="1" t="n"/>
-      <c r="P17" s="1" t="n"/>
-      <c r="Q17" s="1" t="n"/>
-      <c r="R17" s="1" t="n"/>
-      <c r="S17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -22601,14 +22457,6 @@
       <c r="I18" s="1" t="n"/>
       <c r="J18" s="1" t="n"/>
       <c r="K18" s="1" t="n"/>
-      <c r="L18" s="1" t="n"/>
-      <c r="M18" s="1" t="n"/>
-      <c r="N18" s="1" t="n"/>
-      <c r="O18" s="1" t="n"/>
-      <c r="P18" s="1" t="n"/>
-      <c r="Q18" s="1" t="n"/>
-      <c r="R18" s="1" t="n"/>
-      <c r="S18" s="1" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
@@ -22626,14 +22474,6 @@
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -22691,14 +22531,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr"/>
@@ -22752,14 +22584,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr"/>
@@ -22805,14 +22629,6 @@
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr"/>
-      <c r="L22" s="1" t="n"/>
-      <c r="M22" s="1" t="n"/>
-      <c r="N22" s="1" t="n"/>
-      <c r="O22" s="1" t="n"/>
-      <c r="P22" s="1" t="n"/>
-      <c r="Q22" s="1" t="n"/>
-      <c r="R22" s="1" t="n"/>
-      <c r="S22" s="1" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr"/>
@@ -22858,14 +22674,6 @@
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr"/>
-      <c r="L23" s="1" t="n"/>
-      <c r="M23" s="1" t="n"/>
-      <c r="N23" s="1" t="n"/>
-      <c r="O23" s="1" t="n"/>
-      <c r="P23" s="1" t="n"/>
-      <c r="Q23" s="1" t="n"/>
-      <c r="R23" s="1" t="n"/>
-      <c r="S23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr"/>
@@ -22911,14 +22719,6 @@
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr"/>
-      <c r="L24" s="1" t="n"/>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="1" t="n"/>
-      <c r="O24" s="1" t="n"/>
-      <c r="P24" s="1" t="n"/>
-      <c r="Q24" s="1" t="n"/>
-      <c r="R24" s="1" t="n"/>
-      <c r="S24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr"/>
@@ -22964,14 +22764,6 @@
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr"/>
-      <c r="L25" s="1" t="n"/>
-      <c r="M25" s="1" t="n"/>
-      <c r="N25" s="1" t="n"/>
-      <c r="O25" s="1" t="n"/>
-      <c r="P25" s="1" t="n"/>
-      <c r="Q25" s="1" t="n"/>
-      <c r="R25" s="1" t="n"/>
-      <c r="S25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr"/>
@@ -23017,14 +22809,6 @@
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr"/>
-      <c r="L26" s="1" t="n"/>
-      <c r="M26" s="1" t="n"/>
-      <c r="N26" s="1" t="n"/>
-      <c r="O26" s="1" t="n"/>
-      <c r="P26" s="1" t="n"/>
-      <c r="Q26" s="1" t="n"/>
-      <c r="R26" s="1" t="n"/>
-      <c r="S26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -23038,14 +22822,6 @@
       <c r="I27" s="1" t="n"/>
       <c r="J27" s="1" t="n"/>
       <c r="K27" s="1" t="n"/>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="1" t="n"/>
-      <c r="O27" s="1" t="n"/>
-      <c r="P27" s="1" t="n"/>
-      <c r="Q27" s="1" t="n"/>
-      <c r="R27" s="1" t="n"/>
-      <c r="S27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr"/>
@@ -23063,14 +22839,6 @@
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
-      <c r="O28" s="4" t="n"/>
-      <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n"/>
-      <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -23128,14 +22896,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr"/>
@@ -23189,14 +22949,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr"/>
@@ -23222,7 +22974,7 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Синий бутон</t>
+          <t>синий бутон для бутоньерки</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
@@ -23246,14 +22998,6 @@
         </is>
       </c>
       <c r="K31" s="1" t="inlineStr"/>
-      <c r="L31" s="1" t="n"/>
-      <c r="M31" s="1" t="n"/>
-      <c r="N31" s="1" t="n"/>
-      <c r="O31" s="1" t="n"/>
-      <c r="P31" s="1" t="n"/>
-      <c r="Q31" s="1" t="n"/>
-      <c r="R31" s="1" t="n"/>
-      <c r="S31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr"/>
@@ -23279,7 +23023,7 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Ароматная капля</t>
+          <t>ароматную каплю для котла</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
@@ -23303,14 +23047,6 @@
         </is>
       </c>
       <c r="K32" s="1" t="inlineStr"/>
-      <c r="L32" s="1" t="n"/>
-      <c r="M32" s="1" t="n"/>
-      <c r="N32" s="1" t="n"/>
-      <c r="O32" s="1" t="n"/>
-      <c r="P32" s="1" t="n"/>
-      <c r="Q32" s="1" t="n"/>
-      <c r="R32" s="1" t="n"/>
-      <c r="S32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr"/>
@@ -23336,7 +23072,7 @@
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>Синяя лента</t>
+          <t>синяя болотная лента</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
@@ -23360,14 +23096,6 @@
         </is>
       </c>
       <c r="K33" s="1" t="inlineStr"/>
-      <c r="L33" s="1" t="n"/>
-      <c r="M33" s="1" t="n"/>
-      <c r="N33" s="1" t="n"/>
-      <c r="O33" s="1" t="n"/>
-      <c r="P33" s="1" t="n"/>
-      <c r="Q33" s="1" t="n"/>
-      <c r="R33" s="1" t="n"/>
-      <c r="S33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr"/>
@@ -23393,7 +23121,7 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>Серебряная застёжка</t>
+          <t>серебряную застёжку для фляги</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -23417,14 +23145,6 @@
         </is>
       </c>
       <c r="K34" s="1" t="inlineStr"/>
-      <c r="L34" s="1" t="n"/>
-      <c r="M34" s="1" t="n"/>
-      <c r="N34" s="1" t="n"/>
-      <c r="O34" s="1" t="n"/>
-      <c r="P34" s="1" t="n"/>
-      <c r="Q34" s="1" t="n"/>
-      <c r="R34" s="1" t="n"/>
-      <c r="S34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr"/>
@@ -23450,7 +23170,7 @@
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Мягкий настил</t>
+          <t>семицветный огонёк для шалаша</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -23474,14 +23194,6 @@
         </is>
       </c>
       <c r="K35" s="1" t="inlineStr"/>
-      <c r="L35" s="1" t="n"/>
-      <c r="M35" s="1" t="n"/>
-      <c r="N35" s="1" t="n"/>
-      <c r="O35" s="1" t="n"/>
-      <c r="P35" s="1" t="n"/>
-      <c r="Q35" s="1" t="n"/>
-      <c r="R35" s="1" t="n"/>
-      <c r="S35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
@@ -23495,14 +23207,6 @@
       <c r="I36" s="1" t="n"/>
       <c r="J36" s="1" t="n"/>
       <c r="K36" s="1" t="n"/>
-      <c r="L36" s="1" t="n"/>
-      <c r="M36" s="1" t="n"/>
-      <c r="N36" s="1" t="n"/>
-      <c r="O36" s="1" t="n"/>
-      <c r="P36" s="1" t="n"/>
-      <c r="Q36" s="1" t="n"/>
-      <c r="R36" s="1" t="n"/>
-      <c r="S36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr"/>
@@ -23520,14 +23224,6 @@
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
-      <c r="O37" s="4" t="n"/>
-      <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n"/>
-      <c r="R37" s="4" t="n"/>
-      <c r="S37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -23581,14 +23277,6 @@
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="n"/>
-      <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr"/>
@@ -23638,14 +23326,6 @@
         </is>
       </c>
       <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
-      <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="n"/>
-      <c r="R39" s="3" t="n"/>
-      <c r="S39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr"/>
@@ -23671,7 +23351,7 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>Розовая ложечка</t>
+          <t>розовую мерную ложечку</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -23687,14 +23367,6 @@
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="n"/>
-      <c r="L40" s="1" t="n"/>
-      <c r="M40" s="1" t="n"/>
-      <c r="N40" s="1" t="n"/>
-      <c r="O40" s="1" t="n"/>
-      <c r="P40" s="1" t="n"/>
-      <c r="Q40" s="1" t="n"/>
-      <c r="R40" s="1" t="n"/>
-      <c r="S40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr"/>
@@ -23720,7 +23392,7 @@
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>Занавеска</t>
+          <t>занавеску</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
@@ -23736,14 +23408,6 @@
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="n"/>
-      <c r="L41" s="1" t="n"/>
-      <c r="M41" s="1" t="n"/>
-      <c r="N41" s="1" t="n"/>
-      <c r="O41" s="1" t="n"/>
-      <c r="P41" s="1" t="n"/>
-      <c r="Q41" s="1" t="n"/>
-      <c r="R41" s="1" t="n"/>
-      <c r="S41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
@@ -23757,14 +23421,6 @@
       <c r="I42" s="1" t="n"/>
       <c r="J42" s="1" t="n"/>
       <c r="K42" s="1" t="n"/>
-      <c r="L42" s="1" t="n"/>
-      <c r="M42" s="1" t="n"/>
-      <c r="N42" s="1" t="n"/>
-      <c r="O42" s="1" t="n"/>
-      <c r="P42" s="1" t="n"/>
-      <c r="Q42" s="1" t="n"/>
-      <c r="R42" s="1" t="n"/>
-      <c r="S42" s="1" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr"/>
@@ -23782,14 +23438,6 @@
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
-      <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n"/>
-      <c r="R43" s="4" t="n"/>
-      <c r="S43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -23847,14 +23495,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n"/>
-      <c r="R44" s="2" t="n"/>
-      <c r="S44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr"/>
@@ -23908,14 +23548,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr"/>
@@ -23941,7 +23573,7 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Розовая ложечка</t>
+          <t>розовую мерную ложечку</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -23965,14 +23597,6 @@
         </is>
       </c>
       <c r="K46" s="1" t="inlineStr"/>
-      <c r="L46" s="1" t="n"/>
-      <c r="M46" s="1" t="n"/>
-      <c r="N46" s="1" t="n"/>
-      <c r="O46" s="1" t="n"/>
-      <c r="P46" s="1" t="n"/>
-      <c r="Q46" s="1" t="n"/>
-      <c r="R46" s="1" t="n"/>
-      <c r="S46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr"/>
@@ -23998,7 +23622,7 @@
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>Занавеска</t>
+          <t>занавеску</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -24022,14 +23646,6 @@
         </is>
       </c>
       <c r="K47" s="1" t="inlineStr"/>
-      <c r="L47" s="1" t="n"/>
-      <c r="M47" s="1" t="n"/>
-      <c r="N47" s="1" t="n"/>
-      <c r="O47" s="1" t="n"/>
-      <c r="P47" s="1" t="n"/>
-      <c r="Q47" s="1" t="n"/>
-      <c r="R47" s="1" t="n"/>
-      <c r="S47" s="1" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
@@ -24043,14 +23659,6 @@
       <c r="I48" s="1" t="n"/>
       <c r="J48" s="1" t="n"/>
       <c r="K48" s="1" t="n"/>
-      <c r="L48" s="1" t="n"/>
-      <c r="M48" s="1" t="n"/>
-      <c r="N48" s="1" t="n"/>
-      <c r="O48" s="1" t="n"/>
-      <c r="P48" s="1" t="n"/>
-      <c r="Q48" s="1" t="n"/>
-      <c r="R48" s="1" t="n"/>
-      <c r="S48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr"/>
@@ -24068,14 +23676,6 @@
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
-      <c r="O49" s="4" t="n"/>
-      <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n"/>
-      <c r="R49" s="4" t="n"/>
-      <c r="S49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -24133,14 +23733,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n"/>
-      <c r="Q50" s="2" t="n"/>
-      <c r="R50" s="2" t="n"/>
-      <c r="S50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr"/>
@@ -24194,14 +23786,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="L51" s="3" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
-      <c r="O51" s="3" t="n"/>
-      <c r="P51" s="3" t="n"/>
-      <c r="Q51" s="3" t="n"/>
-      <c r="R51" s="3" t="n"/>
-      <c r="S51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr"/>
@@ -24227,7 +23811,7 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Розовая ложечка</t>
+          <t>розовую мерную ложечку</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -24251,14 +23835,6 @@
         </is>
       </c>
       <c r="K52" s="1" t="inlineStr"/>
-      <c r="L52" s="1" t="n"/>
-      <c r="M52" s="1" t="n"/>
-      <c r="N52" s="1" t="n"/>
-      <c r="O52" s="1" t="n"/>
-      <c r="P52" s="1" t="n"/>
-      <c r="Q52" s="1" t="n"/>
-      <c r="R52" s="1" t="n"/>
-      <c r="S52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr"/>
@@ -24284,7 +23860,7 @@
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>Занавеска</t>
+          <t>занавеску</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
@@ -24308,14 +23884,6 @@
         </is>
       </c>
       <c r="K53" s="1" t="inlineStr"/>
-      <c r="L53" s="1" t="n"/>
-      <c r="M53" s="1" t="n"/>
-      <c r="N53" s="1" t="n"/>
-      <c r="O53" s="1" t="n"/>
-      <c r="P53" s="1" t="n"/>
-      <c r="Q53" s="1" t="n"/>
-      <c r="R53" s="1" t="n"/>
-      <c r="S53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
@@ -24329,14 +23897,6 @@
       <c r="I54" s="1" t="n"/>
       <c r="J54" s="1" t="n"/>
       <c r="K54" s="1" t="n"/>
-      <c r="L54" s="1" t="n"/>
-      <c r="M54" s="1" t="n"/>
-      <c r="N54" s="1" t="n"/>
-      <c r="O54" s="1" t="n"/>
-      <c r="P54" s="1" t="n"/>
-      <c r="Q54" s="1" t="n"/>
-      <c r="R54" s="1" t="n"/>
-      <c r="S54" s="1" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr"/>
@@ -24354,14 +23914,6 @@
       <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
-      <c r="O55" s="4" t="n"/>
-      <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n"/>
-      <c r="R55" s="4" t="n"/>
-      <c r="S55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -24415,14 +23967,6 @@
         </is>
       </c>
       <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
-      <c r="Q56" s="2" t="n"/>
-      <c r="R56" s="2" t="n"/>
-      <c r="S56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr"/>
@@ -24472,14 +24016,6 @@
         </is>
       </c>
       <c r="K57" s="3" t="n"/>
-      <c r="L57" s="3" t="n"/>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="3" t="n"/>
-      <c r="O57" s="3" t="n"/>
-      <c r="P57" s="3" t="n"/>
-      <c r="Q57" s="3" t="n"/>
-      <c r="R57" s="3" t="n"/>
-      <c r="S57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr"/>
@@ -24505,7 +24041,7 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>Заплатка</t>
+          <t>заплатку</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -24521,14 +24057,6 @@
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="n"/>
-      <c r="L58" s="1" t="n"/>
-      <c r="M58" s="1" t="n"/>
-      <c r="N58" s="1" t="n"/>
-      <c r="O58" s="1" t="n"/>
-      <c r="P58" s="1" t="n"/>
-      <c r="Q58" s="1" t="n"/>
-      <c r="R58" s="1" t="n"/>
-      <c r="S58" s="1" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
@@ -24542,14 +24070,6 @@
       <c r="I59" s="1" t="n"/>
       <c r="J59" s="1" t="n"/>
       <c r="K59" s="1" t="n"/>
-      <c r="L59" s="1" t="n"/>
-      <c r="M59" s="1" t="n"/>
-      <c r="N59" s="1" t="n"/>
-      <c r="O59" s="1" t="n"/>
-      <c r="P59" s="1" t="n"/>
-      <c r="Q59" s="1" t="n"/>
-      <c r="R59" s="1" t="n"/>
-      <c r="S59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr"/>
@@ -24567,14 +24087,6 @@
       <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
-      <c r="O60" s="4" t="n"/>
-      <c r="P60" s="4" t="n"/>
-      <c r="Q60" s="4" t="n"/>
-      <c r="R60" s="4" t="n"/>
-      <c r="S60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -24632,14 +24144,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="n"/>
-      <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="n"/>
-      <c r="R61" s="2" t="n"/>
-      <c r="S61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr"/>
@@ -24693,14 +24197,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="L62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
-      <c r="O62" s="3" t="n"/>
-      <c r="P62" s="3" t="n"/>
-      <c r="Q62" s="3" t="n"/>
-      <c r="R62" s="3" t="n"/>
-      <c r="S62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr"/>
@@ -24726,7 +24222,7 @@
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>Заплатка</t>
+          <t>заплатку</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
@@ -24750,14 +24246,6 @@
         </is>
       </c>
       <c r="K63" s="1" t="inlineStr"/>
-      <c r="L63" s="1" t="n"/>
-      <c r="M63" s="1" t="n"/>
-      <c r="N63" s="1" t="n"/>
-      <c r="O63" s="1" t="n"/>
-      <c r="P63" s="1" t="n"/>
-      <c r="Q63" s="1" t="n"/>
-      <c r="R63" s="1" t="n"/>
-      <c r="S63" s="1" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
@@ -24771,14 +24259,6 @@
       <c r="I64" s="1" t="n"/>
       <c r="J64" s="1" t="n"/>
       <c r="K64" s="1" t="n"/>
-      <c r="L64" s="1" t="n"/>
-      <c r="M64" s="1" t="n"/>
-      <c r="N64" s="1" t="n"/>
-      <c r="O64" s="1" t="n"/>
-      <c r="P64" s="1" t="n"/>
-      <c r="Q64" s="1" t="n"/>
-      <c r="R64" s="1" t="n"/>
-      <c r="S64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr"/>
@@ -24796,14 +24276,6 @@
       <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
-      <c r="O65" s="4" t="n"/>
-      <c r="P65" s="4" t="n"/>
-      <c r="Q65" s="4" t="n"/>
-      <c r="R65" s="4" t="n"/>
-      <c r="S65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -24861,14 +24333,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
-      <c r="Q66" s="2" t="n"/>
-      <c r="R66" s="2" t="n"/>
-      <c r="S66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr"/>
@@ -24922,14 +24386,6 @@
           <t>id</t>
         </is>
       </c>
-      <c r="L67" s="3" t="n"/>
-      <c r="M67" s="3" t="n"/>
-      <c r="N67" s="3" t="n"/>
-      <c r="O67" s="3" t="n"/>
-      <c r="P67" s="3" t="n"/>
-      <c r="Q67" s="3" t="n"/>
-      <c r="R67" s="3" t="n"/>
-      <c r="S67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr"/>
@@ -24955,7 +24411,7 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>Заплатка</t>
+          <t>заплатку</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
@@ -24979,14 +24435,6 @@
         </is>
       </c>
       <c r="K68" s="1" t="inlineStr"/>
-      <c r="L68" s="1" t="n"/>
-      <c r="M68" s="1" t="n"/>
-      <c r="N68" s="1" t="n"/>
-      <c r="O68" s="1" t="n"/>
-      <c r="P68" s="1" t="n"/>
-      <c r="Q68" s="1" t="n"/>
-      <c r="R68" s="1" t="n"/>
-      <c r="S68" s="1" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
@@ -25000,14 +24448,6 @@
       <c r="I69" s="1" t="n"/>
       <c r="J69" s="1" t="n"/>
       <c r="K69" s="1" t="n"/>
-      <c r="L69" s="1" t="n"/>
-      <c r="M69" s="1" t="n"/>
-      <c r="N69" s="1" t="n"/>
-      <c r="O69" s="1" t="n"/>
-      <c r="P69" s="1" t="n"/>
-      <c r="Q69" s="1" t="n"/>
-      <c r="R69" s="1" t="n"/>
-      <c r="S69" s="1" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr"/>
@@ -25025,14 +24465,6 @@
       <c r="I70" s="4" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="n"/>
-      <c r="L70" s="4" t="n"/>
-      <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n"/>
-      <c r="O70" s="4" t="n"/>
-      <c r="P70" s="4" t="n"/>
-      <c r="Q70" s="4" t="n"/>
-      <c r="R70" s="4" t="n"/>
-      <c r="S70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -25086,14 +24518,6 @@
         </is>
       </c>
       <c r="K71" s="2" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="2" t="n"/>
-      <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="n"/>
-      <c r="Q71" s="2" t="n"/>
-      <c r="R71" s="2" t="n"/>
-      <c r="S71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr"/>
@@ -25143,14 +24567,6 @@
         </is>
       </c>
       <c r="K72" s="3" t="n"/>
-      <c r="L72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
-      <c r="P72" s="3" t="n"/>
-      <c r="Q72" s="3" t="n"/>
-      <c r="R72" s="3" t="n"/>
-      <c r="S72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr"/>
@@ -25176,7 +24592,7 @@
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>Приличное зелье</t>
+          <t>Приличное зелье первого впечатления</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
@@ -25192,14 +24608,6 @@
       </c>
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="n"/>
-      <c r="L73" s="1" t="n"/>
-      <c r="M73" s="1" t="n"/>
-      <c r="N73" s="1" t="n"/>
-      <c r="O73" s="1" t="n"/>
-      <c r="P73" s="1" t="n"/>
-      <c r="Q73" s="1" t="n"/>
-      <c r="R73" s="1" t="n"/>
-      <c r="S73" s="1" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr"/>
@@ -25225,7 +24633,7 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>Набор</t>
+          <t>Набор для романтического похода</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
@@ -25241,14 +24649,6 @@
       </c>
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="n"/>
-      <c r="L74" s="1" t="n"/>
-      <c r="M74" s="1" t="n"/>
-      <c r="N74" s="1" t="n"/>
-      <c r="O74" s="1" t="n"/>
-      <c r="P74" s="1" t="n"/>
-      <c r="Q74" s="1" t="n"/>
-      <c r="R74" s="1" t="n"/>
-      <c r="S74" s="1" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr"/>
@@ -25274,7 +24674,7 @@
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>Тихий шалаш</t>
+          <t>Тихий шалаш для двоих</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
@@ -25290,513 +24690,6 @@
       </c>
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="n"/>
-      <c r="L75" s="1" t="n"/>
-      <c r="M75" s="1" t="n"/>
-      <c r="N75" s="1" t="n"/>
-      <c r="O75" s="1" t="n"/>
-      <c r="P75" s="1" t="n"/>
-      <c r="Q75" s="1" t="n"/>
-      <c r="R75" s="1" t="n"/>
-      <c r="S75" s="1" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="n"/>
-      <c r="C76" s="1" t="n"/>
-      <c r="D76" s="1" t="n"/>
-      <c r="E76" s="1" t="n"/>
-      <c r="F76" s="1" t="n"/>
-      <c r="G76" s="1" t="n"/>
-      <c r="H76" s="1" t="n"/>
-      <c r="I76" s="1" t="n"/>
-      <c r="J76" s="1" t="n"/>
-      <c r="K76" s="1" t="n"/>
-      <c r="L76" s="1" t="n"/>
-      <c r="M76" s="1" t="n"/>
-      <c r="N76" s="1" t="n"/>
-      <c r="O76" s="1" t="n"/>
-      <c r="P76" s="1" t="n"/>
-      <c r="Q76" s="1" t="n"/>
-      <c r="R76" s="1" t="n"/>
-      <c r="S76" s="1" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr"/>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Рецепты 4 ингридиента</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
-      <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="4" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="4" t="inlineStr"/>
-      <c r="N77" s="4" t="inlineStr"/>
-      <c r="O77" s="4" t="inlineStr"/>
-      <c r="P77" s="4" t="inlineStr"/>
-      <c r="Q77" s="4" t="inlineStr"/>
-      <c r="R77" s="4" t="inlineStr"/>
-      <c r="S77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>temp_01</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>ignore</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr"/>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>identifier</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>lifespan</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>ingredients</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_1_asset</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_1_asset_amount</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_2_asset</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_2_asset_amount</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_3_asset</t>
-        </is>
-      </c>
-      <c r="N79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_3_asset_amount</t>
-        </is>
-      </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_4_asset</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="inlineStr">
-        <is>
-          <t>ingredient_4_asset_amount</t>
-        </is>
-      </c>
-      <c r="Q79" s="3" t="inlineStr">
-        <is>
-          <t>conditions</t>
-        </is>
-      </c>
-      <c r="R79" s="3" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="S79" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>/recipe/Dacha_2025/Dacha_2025_R_1_Recipe.proto.js</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>/recipe/LeshyBachelor_2026/LeshyBachelor_2026_R_1_Recipe.proto.js</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_R_1_Recipe</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_R_1</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>asset=LeshyBachelor_2026_ASK_1:10+asset=LeshyBachelor_2026_GR_2:40+asset=LeshyBachelor_2026_Story_RandomRecipe_1_R_1:1+asset=LeshyBachelor_2026_Story_FA_2:1</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_ASK_1</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_GR_2</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_Story_RandomRecipe_1_R_1</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_Story_FA_2</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>active_quest=LeshyBachelor_2026_Story_3+asset!=LeshyBachelor_2026_R_1:1</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>asset=LeshyBachelor_2026_R_1:1</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>/recipe/Dacha_2025/Dacha_2025_R_1_Recipe.proto.js</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>/recipe/LeshyBachelor_2026/LeshyBachelor_2026_R_2_Recipe.proto.js</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_R_2_Recipe</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_R_2</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026</t>
-        </is>
-      </c>
-      <c r="H81" s="1" t="inlineStr">
-        <is>
-          <t>asset=LeshyBachelor_2026_PER_1:10+asset=LeshyBachelor_2026_GR_4:40+asset=LeshyBachelor_2026_Chest_1_R_1:1+asset=LeshyBachelor_2026_Story_RandomRecipe_1_R_1:1</t>
-        </is>
-      </c>
-      <c r="I81" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_PER_1</t>
-        </is>
-      </c>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_GR_4</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M81" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_Chest_1_R_1</t>
-        </is>
-      </c>
-      <c r="N81" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O81" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_Story_RandomRecipe_1_R_1</t>
-        </is>
-      </c>
-      <c r="P81" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q81" s="1" t="inlineStr">
-        <is>
-          <t>active_quest=LeshyBachelor_2026_Story_7+asset!=LeshyBachelor_2026_R_2:1</t>
-        </is>
-      </c>
-      <c r="R81" s="1" t="inlineStr">
-        <is>
-          <t>asset=LeshyBachelor_2026_R_2:1</t>
-        </is>
-      </c>
-      <c r="S81" s="1" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>/recipe/Dacha_2025/Dacha_2025_R_1_Recipe.proto.js</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>/recipe/LeshyBachelor_2026/LeshyBachelor_2026_R_3_Recipe.proto.js</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_R_3_Recipe</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_R_3</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026</t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>asset=LeshyBachelor_2026_ASK_2:10+asset=LeshyBachelor_2026_GR_5:80+asset=LeshyBachelor_2026_Story_FA_2:1+asset=LeshyBachelor_2026_Chest_1_R_1:1</t>
-        </is>
-      </c>
-      <c r="I82" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_ASK_2</t>
-        </is>
-      </c>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_GR_5</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="M82" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_Story_FA_2</t>
-        </is>
-      </c>
-      <c r="N82" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O82" s="1" t="inlineStr">
-        <is>
-          <t>LeshyBachelor_2026_Chest_1_R_1</t>
-        </is>
-      </c>
-      <c r="P82" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q82" s="1" t="inlineStr">
-        <is>
-          <t>active_quest=LeshyBachelor_2026_Story_11+asset!=LeshyBachelor_2026_R_3:1</t>
-        </is>
-      </c>
-      <c r="R82" s="1" t="inlineStr">
-        <is>
-          <t>asset=LeshyBachelor_2026_R_3:1</t>
-        </is>
-      </c>
-      <c r="S82" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
